--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Market Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I471"/>
+  <dimension ref="A1:I472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22581,6 +22581,53 @@
         </is>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>180,803,676</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>1,954.44755</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>Apr 06, 2026</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>5,122.53162</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>9.10865</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>10.26091</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>4,707.925</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>6,812,534.040</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>149,305</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I472"/>
+  <dimension ref="A1:I473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22628,6 +22628,53 @@
         </is>
       </c>
     </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>180,803,676</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>1,954.44755</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>Apr 06, 2026</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>5,122.53162</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>9.10865</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>10.26091</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>4,707.925</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>6,812,534.040</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>149,305</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I473"/>
+  <dimension ref="A1:I474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22675,6 +22675,53 @@
         </is>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>242,907,690</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>1,971.37283</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>Apr 07, 2026</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>5,156.87358</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>16.92528</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>34.34196</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>5,970.144</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>6,823,198.652</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>168,809</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I474"/>
+  <dimension ref="A1:I475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22722,6 +22722,53 @@
         </is>
       </c>
     </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>242,907,690</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>1,971.37283</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>Apr 07, 2026</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>5,156.87358</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>16.92528</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>34.34196</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>5,970.144</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>6,823,198.652</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr">
+        <is>
+          <t>168,809</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I475"/>
+  <dimension ref="A1:I476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22769,6 +22769,53 @@
         </is>
       </c>
     </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>343,139,154</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>2,026.06164</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>Apr 08, 2026</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>5,317.96198</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>54.68881</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>161.0884</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>9,915.93</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>6,918,966.244</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>243,061</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I476"/>
+  <dimension ref="A1:I477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22816,6 +22816,53 @@
         </is>
       </c>
     </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>343,139,154</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>2,026.06164</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>Apr 08, 2026</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>5,317.96198</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>54.68881</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>161.0884</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>9,915.93</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>6,918,966.244</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>243,061</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I477"/>
+  <dimension ref="A1:I478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22863,6 +22863,53 @@
         </is>
       </c>
     </row>
+    <row r="478">
+      <c r="A478" s="3" t="inlineStr">
+        <is>
+          <t>277,738,268</t>
+        </is>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>2,002.20515</t>
+        </is>
+      </c>
+      <c r="C478" s="3" t="inlineStr">
+        <is>
+          <t>Apr 09, 2026</t>
+        </is>
+      </c>
+      <c r="D478" s="3" t="inlineStr">
+        <is>
+          <t>5,257.70314</t>
+        </is>
+      </c>
+      <c r="E478" s="3" t="inlineStr">
+        <is>
+          <t>-23.85649</t>
+        </is>
+      </c>
+      <c r="F478" s="3" t="inlineStr">
+        <is>
+          <t>-60.25884</t>
+        </is>
+      </c>
+      <c r="G478" s="3" t="inlineStr">
+        <is>
+          <t>7,768.645</t>
+        </is>
+      </c>
+      <c r="H478" s="3" t="inlineStr">
+        <is>
+          <t>6,886,627.425</t>
+        </is>
+      </c>
+      <c r="I478" s="3" t="inlineStr">
+        <is>
+          <t>224,389</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I478"/>
+  <dimension ref="A1:I479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22910,6 +22910,53 @@
         </is>
       </c>
     </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>285,967,079</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>2,002.35166</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>Apr 12, 2026</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>5,271.40025</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>0.14651</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>13.69711</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>8,371.04</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>6,879,326.051</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>217,049</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I479"/>
+  <dimension ref="A1:I480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22957,6 +22957,53 @@
         </is>
       </c>
     </row>
+    <row r="480">
+      <c r="A480" s="3" t="inlineStr">
+        <is>
+          <t>279,933,066</t>
+        </is>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>1,981.04255</t>
+        </is>
+      </c>
+      <c r="C480" s="3" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026</t>
+        </is>
+      </c>
+      <c r="D480" s="3" t="inlineStr">
+        <is>
+          <t>5,230.36589</t>
+        </is>
+      </c>
+      <c r="E480" s="3" t="inlineStr">
+        <is>
+          <t>-21.30911</t>
+        </is>
+      </c>
+      <c r="F480" s="3" t="inlineStr">
+        <is>
+          <t>-41.03436</t>
+        </is>
+      </c>
+      <c r="G480" s="3" t="inlineStr">
+        <is>
+          <t>7,934.264</t>
+        </is>
+      </c>
+      <c r="H480" s="3" t="inlineStr">
+        <is>
+          <t>6,853,768.662</t>
+        </is>
+      </c>
+      <c r="I480" s="3" t="inlineStr">
+        <is>
+          <t>222,205</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I480"/>
+  <dimension ref="A1:I481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23004,6 +23004,53 @@
         </is>
       </c>
     </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>317,654,860</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>1,984.20704</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>5,254.99886</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>3.16449</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>24.63297</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>8,364.843</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>6,855,316.822</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="inlineStr">
+        <is>
+          <t>224,647</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I481"/>
+  <dimension ref="A1:I482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23051,6 +23051,53 @@
         </is>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>317,065,005</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>1,990.22568</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>5,256.83779</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>6.01864</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>1.83893</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>8,061.512</t>
+        </is>
+      </c>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>6,856,315.839</t>
+        </is>
+      </c>
+      <c r="I482" s="2" t="inlineStr">
+        <is>
+          <t>222,104</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I482"/>
+  <dimension ref="A1:I483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23098,6 +23098,53 @@
         </is>
       </c>
     </row>
+    <row r="483">
+      <c r="A483" s="3" t="inlineStr">
+        <is>
+          <t>288,465,068</t>
+        </is>
+      </c>
+      <c r="B483" s="3" t="inlineStr">
+        <is>
+          <t>1,990.31492</t>
+        </is>
+      </c>
+      <c r="C483" s="3" t="inlineStr">
+        <is>
+          <t>Apr 19, 2026</t>
+        </is>
+      </c>
+      <c r="D483" s="3" t="inlineStr">
+        <is>
+          <t>5,247.53612</t>
+        </is>
+      </c>
+      <c r="E483" s="3" t="inlineStr">
+        <is>
+          <t>0.08924</t>
+        </is>
+      </c>
+      <c r="F483" s="3" t="inlineStr">
+        <is>
+          <t>-9.30167</t>
+        </is>
+      </c>
+      <c r="G483" s="3" t="inlineStr">
+        <is>
+          <t>8,192.02</t>
+        </is>
+      </c>
+      <c r="H483" s="3" t="inlineStr">
+        <is>
+          <t>6,847,233.938</t>
+        </is>
+      </c>
+      <c r="I483" s="3" t="inlineStr">
+        <is>
+          <t>214,241</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I483"/>
+  <dimension ref="A1:I484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23145,6 +23145,53 @@
         </is>
       </c>
     </row>
+    <row r="484">
+      <c r="A484" s="3" t="inlineStr">
+        <is>
+          <t>296,361,347</t>
+        </is>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>1,980.00817</t>
+        </is>
+      </c>
+      <c r="C484" s="3" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026</t>
+        </is>
+      </c>
+      <c r="D484" s="3" t="inlineStr">
+        <is>
+          <t>5,232.49056</t>
+        </is>
+      </c>
+      <c r="E484" s="3" t="inlineStr">
+        <is>
+          <t>-10.30675</t>
+        </is>
+      </c>
+      <c r="F484" s="3" t="inlineStr">
+        <is>
+          <t>-15.04556</t>
+        </is>
+      </c>
+      <c r="G484" s="3" t="inlineStr">
+        <is>
+          <t>8,247.602</t>
+        </is>
+      </c>
+      <c r="H484" s="3" t="inlineStr">
+        <is>
+          <t>6,816,224.453</t>
+        </is>
+      </c>
+      <c r="I484" s="3" t="inlineStr">
+        <is>
+          <t>223,903</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I484"/>
+  <dimension ref="A1:I485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23192,6 +23192,53 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>314,461,646</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>1,984.176</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>Apr 21, 2026</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>5,257.41321</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>4.16783</t>
+        </is>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>24.92265</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>9,292.884</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>6,835,972.322</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>246,621</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I485"/>
+  <dimension ref="A1:I486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23239,6 +23239,53 @@
         </is>
       </c>
     </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>358,282,028</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>2,004.5015</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>Apr 22, 2026</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>5,298.5814</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>20.3255</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>41.16819</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>10,563.63</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>6,861,841.794</t>
+        </is>
+      </c>
+      <c r="I486" s="2" t="inlineStr">
+        <is>
+          <t>276,013</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I486"/>
+  <dimension ref="A1:I487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23286,6 +23286,53 @@
         </is>
       </c>
     </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>265,309,759</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>2,014.93557</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>Apr 23, 2026</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>5,298.58582</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>10.43407</t>
+        </is>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
+        <is>
+          <t>0.00442</t>
+        </is>
+      </c>
+      <c r="G487" s="2" t="inlineStr">
+        <is>
+          <t>8,846.208</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>6,875,501.887</t>
+        </is>
+      </c>
+      <c r="I487" s="2" t="inlineStr">
+        <is>
+          <t>237,833</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I487"/>
+  <dimension ref="A1:I488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23333,6 +23333,53 @@
         </is>
       </c>
     </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>312,036,419</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>2,026.29644</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>5,316.18325</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>11.36087</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>17.59743</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="inlineStr">
+        <is>
+          <t>9,824.205</t>
+        </is>
+      </c>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>6,877,032.923</t>
+        </is>
+      </c>
+      <c r="I488" s="2" t="inlineStr">
+        <is>
+          <t>253,698</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I488"/>
+  <dimension ref="A1:I489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23380,6 +23380,53 @@
         </is>
       </c>
     </row>
+    <row r="489">
+      <c r="A489" s="3" t="inlineStr">
+        <is>
+          <t>290,559,104</t>
+        </is>
+      </c>
+      <c r="B489" s="3" t="inlineStr">
+        <is>
+          <t>2,017.74118</t>
+        </is>
+      </c>
+      <c r="C489" s="3" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026</t>
+        </is>
+      </c>
+      <c r="D489" s="3" t="inlineStr">
+        <is>
+          <t>5,300.5724</t>
+        </is>
+      </c>
+      <c r="E489" s="3" t="inlineStr">
+        <is>
+          <t>-8.55526</t>
+        </is>
+      </c>
+      <c r="F489" s="3" t="inlineStr">
+        <is>
+          <t>-15.61085</t>
+        </is>
+      </c>
+      <c r="G489" s="3" t="inlineStr">
+        <is>
+          <t>9,560.103</t>
+        </is>
+      </c>
+      <c r="H489" s="3" t="inlineStr">
+        <is>
+          <t>6,838,023.567</t>
+        </is>
+      </c>
+      <c r="I489" s="3" t="inlineStr">
+        <is>
+          <t>235,384</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I489"/>
+  <dimension ref="A1:I490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23427,6 +23427,53 @@
         </is>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>336,536,644</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>2,016.42422</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>5,308.89402</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>-1.31696</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>8.32162</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>10,267.309</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>6,851,590.931</t>
+        </is>
+      </c>
+      <c r="I490" s="2" t="inlineStr">
+        <is>
+          <t>240,839</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I490"/>
+  <dimension ref="A1:I491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23474,6 +23474,53 @@
         </is>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>307,948,771</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>2,020.28441</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>Apr 29, 2026</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>5,317.3643</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>3.86019</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
+          <t>8.47028</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>8,877.773</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>6,867,697.595</t>
+        </is>
+      </c>
+      <c r="I491" s="2" t="inlineStr">
+        <is>
+          <t>221,703</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I491"/>
+  <dimension ref="A1:I492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23521,6 +23521,53 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" s="3" t="inlineStr">
+        <is>
+          <t>301,216,957</t>
+        </is>
+      </c>
+      <c r="B492" s="3" t="inlineStr">
+        <is>
+          <t>2,017.00689</t>
+        </is>
+      </c>
+      <c r="C492" s="3" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026</t>
+        </is>
+      </c>
+      <c r="D492" s="3" t="inlineStr">
+        <is>
+          <t>5,286.8736</t>
+        </is>
+      </c>
+      <c r="E492" s="3" t="inlineStr">
+        <is>
+          <t>-3.27752</t>
+        </is>
+      </c>
+      <c r="F492" s="3" t="inlineStr">
+        <is>
+          <t>-30.4907</t>
+        </is>
+      </c>
+      <c r="G492" s="3" t="inlineStr">
+        <is>
+          <t>8,640.266</t>
+        </is>
+      </c>
+      <c r="H492" s="3" t="inlineStr">
+        <is>
+          <t>6,851,187.327</t>
+        </is>
+      </c>
+      <c r="I492" s="3" t="inlineStr">
+        <is>
+          <t>218,689</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I492"/>
+  <dimension ref="A1:I493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23568,6 +23568,53 @@
         </is>
       </c>
     </row>
+    <row r="493">
+      <c r="A493" s="3" t="inlineStr">
+        <is>
+          <t>292,604,568</t>
+        </is>
+      </c>
+      <c r="B493" s="3" t="inlineStr">
+        <is>
+          <t>2,018.88926</t>
+        </is>
+      </c>
+      <c r="C493" s="3" t="inlineStr">
+        <is>
+          <t>May 03, 2026</t>
+        </is>
+      </c>
+      <c r="D493" s="3" t="inlineStr">
+        <is>
+          <t>5,265.39264</t>
+        </is>
+      </c>
+      <c r="E493" s="3" t="inlineStr">
+        <is>
+          <t>1.88237</t>
+        </is>
+      </c>
+      <c r="F493" s="3" t="inlineStr">
+        <is>
+          <t>-21.48096</t>
+        </is>
+      </c>
+      <c r="G493" s="3" t="inlineStr">
+        <is>
+          <t>8,293.753</t>
+        </is>
+      </c>
+      <c r="H493" s="3" t="inlineStr">
+        <is>
+          <t>6,862,146.397</t>
+        </is>
+      </c>
+      <c r="I493" s="3" t="inlineStr">
+        <is>
+          <t>219,332</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I493"/>
+  <dimension ref="A1:I494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23615,6 +23615,53 @@
         </is>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>300,970,675</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>2,023.04412</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>May 04, 2026</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>5,277.80549</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>4.15486</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>12.41285</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>8,769.513</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>6,810,395.274</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="inlineStr">
+        <is>
+          <t>214,652</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I494"/>
+  <dimension ref="A1:I495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23662,6 +23662,53 @@
         </is>
       </c>
     </row>
+    <row r="495">
+      <c r="A495" s="3" t="inlineStr">
+        <is>
+          <t>265,856,598</t>
+        </is>
+      </c>
+      <c r="B495" s="3" t="inlineStr">
+        <is>
+          <t>2,017.16298</t>
+        </is>
+      </c>
+      <c r="C495" s="3" t="inlineStr">
+        <is>
+          <t>May 05, 2026</t>
+        </is>
+      </c>
+      <c r="D495" s="3" t="inlineStr">
+        <is>
+          <t>5,267.22628</t>
+        </is>
+      </c>
+      <c r="E495" s="3" t="inlineStr">
+        <is>
+          <t>-5.88114</t>
+        </is>
+      </c>
+      <c r="F495" s="3" t="inlineStr">
+        <is>
+          <t>-10.57921</t>
+        </is>
+      </c>
+      <c r="G495" s="3" t="inlineStr">
+        <is>
+          <t>8,322.939</t>
+        </is>
+      </c>
+      <c r="H495" s="3" t="inlineStr">
+        <is>
+          <t>6,803,066.374</t>
+        </is>
+      </c>
+      <c r="I495" s="3" t="inlineStr">
+        <is>
+          <t>218,863</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I495"/>
+  <dimension ref="A1:I496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23709,6 +23709,53 @@
         </is>
       </c>
     </row>
+    <row r="496">
+      <c r="A496" s="3" t="inlineStr">
+        <is>
+          <t>247,276,433</t>
+        </is>
+      </c>
+      <c r="B496" s="3" t="inlineStr">
+        <is>
+          <t>2,009.08592</t>
+        </is>
+      </c>
+      <c r="C496" s="3" t="inlineStr">
+        <is>
+          <t>May 06, 2026</t>
+        </is>
+      </c>
+      <c r="D496" s="3" t="inlineStr">
+        <is>
+          <t>5,248.36846</t>
+        </is>
+      </c>
+      <c r="E496" s="3" t="inlineStr">
+        <is>
+          <t>-8.07706</t>
+        </is>
+      </c>
+      <c r="F496" s="3" t="inlineStr">
+        <is>
+          <t>-18.85782</t>
+        </is>
+      </c>
+      <c r="G496" s="3" t="inlineStr">
+        <is>
+          <t>7,676.832</t>
+        </is>
+      </c>
+      <c r="H496" s="3" t="inlineStr">
+        <is>
+          <t>6,799,076.525</t>
+        </is>
+      </c>
+      <c r="I496" s="3" t="inlineStr">
+        <is>
+          <t>210,728</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I496"/>
+  <dimension ref="A1:I497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23756,6 +23756,53 @@
         </is>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" s="3" t="inlineStr">
+        <is>
+          <t>251,970,134</t>
+        </is>
+      </c>
+      <c r="B497" s="3" t="inlineStr">
+        <is>
+          <t>2,001.61062</t>
+        </is>
+      </c>
+      <c r="C497" s="3" t="inlineStr">
+        <is>
+          <t>May 07, 2026</t>
+        </is>
+      </c>
+      <c r="D497" s="3" t="inlineStr">
+        <is>
+          <t>5,234.10034</t>
+        </is>
+      </c>
+      <c r="E497" s="3" t="inlineStr">
+        <is>
+          <t>-7.4753</t>
+        </is>
+      </c>
+      <c r="F497" s="3" t="inlineStr">
+        <is>
+          <t>-14.26812</t>
+        </is>
+      </c>
+      <c r="G497" s="3" t="inlineStr">
+        <is>
+          <t>8,449.295</t>
+        </is>
+      </c>
+      <c r="H497" s="3" t="inlineStr">
+        <is>
+          <t>6,799,949.473</t>
+        </is>
+      </c>
+      <c r="I497" s="3" t="inlineStr">
+        <is>
+          <t>221,546</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I497"/>
+  <dimension ref="A1:I498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23803,6 +23803,53 @@
         </is>
       </c>
     </row>
+    <row r="498">
+      <c r="A498" s="3" t="inlineStr">
+        <is>
+          <t>247,352,065</t>
+        </is>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>1,990.26831</t>
+        </is>
+      </c>
+      <c r="C498" s="3" t="inlineStr">
+        <is>
+          <t>May 10, 2026</t>
+        </is>
+      </c>
+      <c r="D498" s="3" t="inlineStr">
+        <is>
+          <t>5,220.94656</t>
+        </is>
+      </c>
+      <c r="E498" s="3" t="inlineStr">
+        <is>
+          <t>-11.34231</t>
+        </is>
+      </c>
+      <c r="F498" s="3" t="inlineStr">
+        <is>
+          <t>-13.15378</t>
+        </is>
+      </c>
+      <c r="G498" s="3" t="inlineStr">
+        <is>
+          <t>7,274.56</t>
+        </is>
+      </c>
+      <c r="H498" s="3" t="inlineStr">
+        <is>
+          <t>6,764,558.344</t>
+        </is>
+      </c>
+      <c r="I498" s="3" t="inlineStr">
+        <is>
+          <t>210,620</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I498"/>
+  <dimension ref="A1:I499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23850,6 +23850,53 @@
         </is>
       </c>
     </row>
+    <row r="499">
+      <c r="A499" s="3" t="inlineStr">
+        <is>
+          <t>282,096,184</t>
+        </is>
+      </c>
+      <c r="B499" s="3" t="inlineStr">
+        <is>
+          <t>1,985.04126</t>
+        </is>
+      </c>
+      <c r="C499" s="3" t="inlineStr">
+        <is>
+          <t>May 11, 2026</t>
+        </is>
+      </c>
+      <c r="D499" s="3" t="inlineStr">
+        <is>
+          <t>5,205.26311</t>
+        </is>
+      </c>
+      <c r="E499" s="3" t="inlineStr">
+        <is>
+          <t>-5.22705</t>
+        </is>
+      </c>
+      <c r="F499" s="3" t="inlineStr">
+        <is>
+          <t>-15.68345</t>
+        </is>
+      </c>
+      <c r="G499" s="3" t="inlineStr">
+        <is>
+          <t>7,149.757</t>
+        </is>
+      </c>
+      <c r="H499" s="3" t="inlineStr">
+        <is>
+          <t>6,745,613.074</t>
+        </is>
+      </c>
+      <c r="I499" s="3" t="inlineStr">
+        <is>
+          <t>213,966</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I499"/>
+  <dimension ref="A1:I500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23897,6 +23897,53 @@
         </is>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>285,817,571</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>1,989.17933</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>May 12, 2026</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>5,229.95888</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>4.13807</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>24.69577</t>
+        </is>
+      </c>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>11,015.246</t>
+        </is>
+      </c>
+      <c r="H500" s="2" t="inlineStr">
+        <is>
+          <t>6,750,429.001</t>
+        </is>
+      </c>
+      <c r="I500" s="2" t="inlineStr">
+        <is>
+          <t>218,174</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I500"/>
+  <dimension ref="A1:I501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23944,6 +23944,53 @@
         </is>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>288,361,539</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>1,990.71714</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>May 13, 2026</t>
+        </is>
+      </c>
+      <c r="D501" s="2" t="inlineStr">
+        <is>
+          <t>5,243.4345</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>1.53781</t>
+        </is>
+      </c>
+      <c r="F501" s="2" t="inlineStr">
+        <is>
+          <t>13.47562</t>
+        </is>
+      </c>
+      <c r="G501" s="2" t="inlineStr">
+        <is>
+          <t>8,560.977</t>
+        </is>
+      </c>
+      <c r="H501" s="2" t="inlineStr">
+        <is>
+          <t>6,759,413.975</t>
+        </is>
+      </c>
+      <c r="I501" s="2" t="inlineStr">
+        <is>
+          <t>220,886</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I501"/>
+  <dimension ref="A1:I502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23991,6 +23991,53 @@
         </is>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>344,594,966</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>1,981.66948</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>May 14, 2026</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>5,245.22272</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>-9.04766</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>1.78822</t>
+        </is>
+      </c>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>9,973.002</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="inlineStr">
+        <is>
+          <t>6,773,369.714</t>
+        </is>
+      </c>
+      <c r="I502" s="2" t="inlineStr">
+        <is>
+          <t>244,577</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I502"/>
+  <dimension ref="A1:I503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24038,6 +24038,53 @@
         </is>
       </c>
     </row>
+    <row r="503">
+      <c r="A503" s="3" t="inlineStr">
+        <is>
+          <t>293,874,688</t>
+        </is>
+      </c>
+      <c r="B503" s="3" t="inlineStr">
+        <is>
+          <t>1,970.55928</t>
+        </is>
+      </c>
+      <c r="C503" s="3" t="inlineStr">
+        <is>
+          <t>May 17, 2026</t>
+        </is>
+      </c>
+      <c r="D503" s="3" t="inlineStr">
+        <is>
+          <t>5,226.18365</t>
+        </is>
+      </c>
+      <c r="E503" s="3" t="inlineStr">
+        <is>
+          <t>-11.1102</t>
+        </is>
+      </c>
+      <c r="F503" s="3" t="inlineStr">
+        <is>
+          <t>-19.03907</t>
+        </is>
+      </c>
+      <c r="G503" s="3" t="inlineStr">
+        <is>
+          <t>8,682.32</t>
+        </is>
+      </c>
+      <c r="H503" s="3" t="inlineStr">
+        <is>
+          <t>6,763,073.506</t>
+        </is>
+      </c>
+      <c r="I503" s="3" t="inlineStr">
+        <is>
+          <t>226,769</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I503"/>
+  <dimension ref="A1:I504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24085,6 +24085,53 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="3" t="inlineStr">
+        <is>
+          <t>248,366,510</t>
+        </is>
+      </c>
+      <c r="B504" s="3" t="inlineStr">
+        <is>
+          <t>1,968.39544</t>
+        </is>
+      </c>
+      <c r="C504" s="3" t="inlineStr">
+        <is>
+          <t>May 18, 2026</t>
+        </is>
+      </c>
+      <c r="D504" s="3" t="inlineStr">
+        <is>
+          <t>5,203.11208</t>
+        </is>
+      </c>
+      <c r="E504" s="3" t="inlineStr">
+        <is>
+          <t>-2.16384</t>
+        </is>
+      </c>
+      <c r="F504" s="3" t="inlineStr">
+        <is>
+          <t>-23.07157</t>
+        </is>
+      </c>
+      <c r="G504" s="3" t="inlineStr">
+        <is>
+          <t>7,260.831</t>
+        </is>
+      </c>
+      <c r="H504" s="3" t="inlineStr">
+        <is>
+          <t>6,753,298.940</t>
+        </is>
+      </c>
+      <c r="I504" s="3" t="inlineStr">
+        <is>
+          <t>208,744</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I504"/>
+  <dimension ref="A1:I505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24132,6 +24132,53 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>229,913,162</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>1,970.19483</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>May 19, 2026</t>
+        </is>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
+        <is>
+          <t>5,211.54156</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>1.79939</t>
+        </is>
+      </c>
+      <c r="F505" s="2" t="inlineStr">
+        <is>
+          <t>8.42948</t>
+        </is>
+      </c>
+      <c r="G505" s="2" t="inlineStr">
+        <is>
+          <t>6,757.341</t>
+        </is>
+      </c>
+      <c r="H505" s="2" t="inlineStr">
+        <is>
+          <t>6,755,127.860</t>
+        </is>
+      </c>
+      <c r="I505" s="2" t="inlineStr">
+        <is>
+          <t>188,070</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I505"/>
+  <dimension ref="A1:I506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24179,6 +24179,53 @@
         </is>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>302,478,211</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>1,974.81439</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>May 20, 2026</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>5,222.38191</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>4.61956</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>10.84035</t>
+        </is>
+      </c>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>8,411.223</t>
+        </is>
+      </c>
+      <c r="H506" s="2" t="inlineStr">
+        <is>
+          <t>6,754,248.988</t>
+        </is>
+      </c>
+      <c r="I506" s="2" t="inlineStr">
+        <is>
+          <t>219,127</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I506"/>
+  <dimension ref="A1:I507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24226,6 +24226,53 @@
         </is>
       </c>
     </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>274,564,178</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>1,995.35327</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>May 21, 2026</t>
+        </is>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>5,264.12281</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>20.53888</t>
+        </is>
+      </c>
+      <c r="F507" s="2" t="inlineStr">
+        <is>
+          <t>41.7409</t>
+        </is>
+      </c>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>8,674.837</t>
+        </is>
+      </c>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>6,798,194.222</t>
+        </is>
+      </c>
+      <c r="I507" s="2" t="inlineStr">
+        <is>
+          <t>223,270</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I507"/>
+  <dimension ref="A1:I508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24273,6 +24273,53 @@
         </is>
       </c>
     </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>288,573,993</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>2,030.33836</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>May 23, 2026</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>5,328.35993</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>34.98509</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>64.23712</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>9,021.587</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>6,852,330.470</t>
+        </is>
+      </c>
+      <c r="I508" s="2" t="inlineStr">
+        <is>
+          <t>224,236</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I508"/>
+  <dimension ref="A1:I509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24320,6 +24320,53 @@
         </is>
       </c>
     </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>256,424,694</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>2,030.87961</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>May 24, 2026</t>
+        </is>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
+        <is>
+          <t>5,335.86964</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>0.54125</t>
+        </is>
+      </c>
+      <c r="F509" s="2" t="inlineStr">
+        <is>
+          <t>7.50971</t>
+        </is>
+      </c>
+      <c r="G509" s="2" t="inlineStr">
+        <is>
+          <t>7,787.163</t>
+        </is>
+      </c>
+      <c r="H509" s="2" t="inlineStr">
+        <is>
+          <t>6,844,332.455</t>
+        </is>
+      </c>
+      <c r="I509" s="2" t="inlineStr">
+        <is>
+          <t>210,904</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I509"/>
+  <dimension ref="A1:I510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24367,6 +24367,53 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>326,010,531</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>2,044.58769</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>Jun 01, 2026</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>5,372.63439</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>13.70808</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>36.76475</t>
+        </is>
+      </c>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>9,123.874</t>
+        </is>
+      </c>
+      <c r="H510" s="2" t="inlineStr">
+        <is>
+          <t>6,877,052.315</t>
+        </is>
+      </c>
+      <c r="I510" s="2" t="inlineStr">
+        <is>
+          <t>227,730</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I510"/>
+  <dimension ref="A1:I511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24414,6 +24414,53 @@
         </is>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>372,034,387</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>2,049.79559</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="inlineStr">
+        <is>
+          <t>Jun 02, 2026</t>
+        </is>
+      </c>
+      <c r="D511" s="2" t="inlineStr">
+        <is>
+          <t>5,406.20347</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>5.2079</t>
+        </is>
+      </c>
+      <c r="F511" s="2" t="inlineStr">
+        <is>
+          <t>33.56908</t>
+        </is>
+      </c>
+      <c r="G511" s="2" t="inlineStr">
+        <is>
+          <t>10,804.209</t>
+        </is>
+      </c>
+      <c r="H511" s="2" t="inlineStr">
+        <is>
+          <t>6,880,908.914</t>
+        </is>
+      </c>
+      <c r="I511" s="2" t="inlineStr">
+        <is>
+          <t>266,227</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I511"/>
+  <dimension ref="A1:I512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24461,6 +24461,53 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>423,449,169</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>2,057.14601</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>Jun 03, 2026</t>
+        </is>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>5,441.6609</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>7.35042</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>35.45743</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>12,791.321</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>6,893,639.293</t>
+        </is>
+      </c>
+      <c r="I512" s="2" t="inlineStr">
+        <is>
+          <t>316,692</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I512"/>
+  <dimension ref="A1:I513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24508,6 +24508,53 @@
         </is>
       </c>
     </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>431,451,919</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>2,068.33767</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>Jun 04, 2026</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>5,475.00196</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>11.19166</t>
+        </is>
+      </c>
+      <c r="F513" s="2" t="inlineStr">
+        <is>
+          <t>33.34106</t>
+        </is>
+      </c>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>13,515.935</t>
+        </is>
+      </c>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>6,929,761.857</t>
+        </is>
+      </c>
+      <c r="I513" s="2" t="inlineStr">
+        <is>
+          <t>327,629</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I513"/>
+  <dimension ref="A1:I514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24555,6 +24555,53 @@
         </is>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>483,609,338</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>2,087.19876</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>Jun 07, 2026</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>5,516.15981</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>18.86109</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>41.15785</t>
+        </is>
+      </c>
+      <c r="G514" s="2" t="inlineStr">
+        <is>
+          <t>15,290.55</t>
+        </is>
+      </c>
+      <c r="H514" s="2" t="inlineStr">
+        <is>
+          <t>6,921,750.397</t>
+        </is>
+      </c>
+      <c r="I514" s="2" t="inlineStr">
+        <is>
+          <t>358,170</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I514"/>
+  <dimension ref="A1:I515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24602,6 +24602,53 @@
         </is>
       </c>
     </row>
+    <row r="515">
+      <c r="A515" s="3" t="inlineStr">
+        <is>
+          <t>324,403,098</t>
+        </is>
+      </c>
+      <c r="B515" s="3" t="inlineStr">
+        <is>
+          <t>2,069.15088</t>
+        </is>
+      </c>
+      <c r="C515" s="3" t="inlineStr">
+        <is>
+          <t>Jun 08, 2026</t>
+        </is>
+      </c>
+      <c r="D515" s="3" t="inlineStr">
+        <is>
+          <t>5,482.99805</t>
+        </is>
+      </c>
+      <c r="E515" s="3" t="inlineStr">
+        <is>
+          <t>-18.04788</t>
+        </is>
+      </c>
+      <c r="F515" s="3" t="inlineStr">
+        <is>
+          <t>-33.16176</t>
+        </is>
+      </c>
+      <c r="G515" s="3" t="inlineStr">
+        <is>
+          <t>10,724.611</t>
+        </is>
+      </c>
+      <c r="H515" s="3" t="inlineStr">
+        <is>
+          <t>6,905,749.222</t>
+        </is>
+      </c>
+      <c r="I515" s="3" t="inlineStr">
+        <is>
+          <t>274,111</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I515"/>
+  <dimension ref="A1:I516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24649,6 +24649,53 @@
         </is>
       </c>
     </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>390,143,268</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>2,080.14332</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>Jun 09, 2026</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>5,519.48793</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>10.99244</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>36.48988</t>
+        </is>
+      </c>
+      <c r="G516" s="2" t="inlineStr">
+        <is>
+          <t>13,878.466</t>
+        </is>
+      </c>
+      <c r="H516" s="2" t="inlineStr">
+        <is>
+          <t>6,916,049.374</t>
+        </is>
+      </c>
+      <c r="I516" s="2" t="inlineStr">
+        <is>
+          <t>312,308</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I516"/>
+  <dimension ref="A1:I517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24696,6 +24696,53 @@
         </is>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" s="3" t="inlineStr">
+        <is>
+          <t>390,658,769</t>
+        </is>
+      </c>
+      <c r="B517" s="3" t="inlineStr">
+        <is>
+          <t>2,080.09329</t>
+        </is>
+      </c>
+      <c r="C517" s="3" t="inlineStr">
+        <is>
+          <t>Jun 10, 2026</t>
+        </is>
+      </c>
+      <c r="D517" s="3" t="inlineStr">
+        <is>
+          <t>5,516.82363</t>
+        </is>
+      </c>
+      <c r="E517" s="3" t="inlineStr">
+        <is>
+          <t>-0.05003</t>
+        </is>
+      </c>
+      <c r="F517" s="3" t="inlineStr">
+        <is>
+          <t>-2.6643</t>
+        </is>
+      </c>
+      <c r="G517" s="3" t="inlineStr">
+        <is>
+          <t>12,100.551</t>
+        </is>
+      </c>
+      <c r="H517" s="3" t="inlineStr">
+        <is>
+          <t>6,904,636.600</t>
+        </is>
+      </c>
+      <c r="I517" s="3" t="inlineStr">
+        <is>
+          <t>288,152</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I517"/>
+  <dimension ref="A1:I518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24743,6 +24743,53 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>438,313,580</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>2,119.80944</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>Jun 14, 2026</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>5,625.34791</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>46.89977</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>104.95135</t>
+        </is>
+      </c>
+      <c r="G518" s="2" t="inlineStr">
+        <is>
+          <t>13,584.71</t>
+        </is>
+      </c>
+      <c r="H518" s="2" t="inlineStr">
+        <is>
+          <t>6,963,031.930</t>
+        </is>
+      </c>
+      <c r="I518" s="2" t="inlineStr">
+        <is>
+          <t>311,457</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I518"/>
+  <dimension ref="A1:I519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24790,6 +24790,53 @@
         </is>
       </c>
     </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>491,546,209</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>2,128.14205</t>
+        </is>
+      </c>
+      <c r="C519" s="2" t="inlineStr">
+        <is>
+          <t>Jun 15, 2026</t>
+        </is>
+      </c>
+      <c r="D519" s="2" t="inlineStr">
+        <is>
+          <t>5,640.75529</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="inlineStr">
+        <is>
+          <t>8.33261</t>
+        </is>
+      </c>
+      <c r="F519" s="2" t="inlineStr">
+        <is>
+          <t>15.40738</t>
+        </is>
+      </c>
+      <c r="G519" s="2" t="inlineStr">
+        <is>
+          <t>14,561.236</t>
+        </is>
+      </c>
+      <c r="H519" s="2" t="inlineStr">
+        <is>
+          <t>6,970,102.116</t>
+        </is>
+      </c>
+      <c r="I519" s="2" t="inlineStr">
+        <is>
+          <t>326,336</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I519"/>
+  <dimension ref="A1:I520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24837,6 +24837,53 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" s="3" t="inlineStr">
+        <is>
+          <t>416,350,999</t>
+        </is>
+      </c>
+      <c r="B520" s="3" t="inlineStr">
+        <is>
+          <t>2,110.31014</t>
+        </is>
+      </c>
+      <c r="C520" s="3" t="inlineStr">
+        <is>
+          <t>Jun 16, 2026</t>
+        </is>
+      </c>
+      <c r="D520" s="3" t="inlineStr">
+        <is>
+          <t>5,605.57347</t>
+        </is>
+      </c>
+      <c r="E520" s="3" t="inlineStr">
+        <is>
+          <t>-17.83191</t>
+        </is>
+      </c>
+      <c r="F520" s="3" t="inlineStr">
+        <is>
+          <t>-35.18182</t>
+        </is>
+      </c>
+      <c r="G520" s="3" t="inlineStr">
+        <is>
+          <t>11,961.123</t>
+        </is>
+      </c>
+      <c r="H520" s="3" t="inlineStr">
+        <is>
+          <t>6,893,455.454</t>
+        </is>
+      </c>
+      <c r="I520" s="3" t="inlineStr">
+        <is>
+          <t>278,894</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I520"/>
+  <dimension ref="A1:I521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24884,6 +24884,53 @@
         </is>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>436,237,110</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="inlineStr">
+        <is>
+          <t>2,113.0473</t>
+        </is>
+      </c>
+      <c r="C521" s="2" t="inlineStr">
+        <is>
+          <t>Jun 17, 2026</t>
+        </is>
+      </c>
+      <c r="D521" s="2" t="inlineStr">
+        <is>
+          <t>5,621.62554</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="inlineStr">
+        <is>
+          <t>2.73716</t>
+        </is>
+      </c>
+      <c r="F521" s="2" t="inlineStr">
+        <is>
+          <t>16.05207</t>
+        </is>
+      </c>
+      <c r="G521" s="2" t="inlineStr">
+        <is>
+          <t>12,112.955</t>
+        </is>
+      </c>
+      <c r="H521" s="2" t="inlineStr">
+        <is>
+          <t>6,898,187.672</t>
+        </is>
+      </c>
+      <c r="I521" s="2" t="inlineStr">
+        <is>
+          <t>285,669</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I521"/>
+  <dimension ref="A1:I522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24931,6 +24931,53 @@
         </is>
       </c>
     </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>438,328,313</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>2,143.12038</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>Jun 18, 2026</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>5,661.38328</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>30.07308</t>
+        </is>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
+        <is>
+          <t>39.75774</t>
+        </is>
+      </c>
+      <c r="G522" s="2" t="inlineStr">
+        <is>
+          <t>11,972.115</t>
+        </is>
+      </c>
+      <c r="H522" s="2" t="inlineStr">
+        <is>
+          <t>6,934,408.044</t>
+        </is>
+      </c>
+      <c r="I522" s="2" t="inlineStr">
+        <is>
+          <t>273,343</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I522"/>
+  <dimension ref="A1:I523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24978,6 +24978,53 @@
         </is>
       </c>
     </row>
+    <row r="523">
+      <c r="A523" s="3" t="inlineStr">
+        <is>
+          <t>328,592,120</t>
+        </is>
+      </c>
+      <c r="B523" s="3" t="inlineStr">
+        <is>
+          <t>2,145.53512</t>
+        </is>
+      </c>
+      <c r="C523" s="3" t="inlineStr">
+        <is>
+          <t>Jun 21, 2026</t>
+        </is>
+      </c>
+      <c r="D523" s="3" t="inlineStr">
+        <is>
+          <t>5,639.89379</t>
+        </is>
+      </c>
+      <c r="E523" s="3" t="inlineStr">
+        <is>
+          <t>2.41474</t>
+        </is>
+      </c>
+      <c r="F523" s="3" t="inlineStr">
+        <is>
+          <t>-21.48949</t>
+        </is>
+      </c>
+      <c r="G523" s="3" t="inlineStr">
+        <is>
+          <t>10,024.378</t>
+        </is>
+      </c>
+      <c r="H523" s="3" t="inlineStr">
+        <is>
+          <t>6,928,539.270</t>
+        </is>
+      </c>
+      <c r="I523" s="3" t="inlineStr">
+        <is>
+          <t>251,939</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I523"/>
+  <dimension ref="A1:I524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25025,6 +25025,53 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" s="3" t="inlineStr">
+        <is>
+          <t>287,063,880</t>
+        </is>
+      </c>
+      <c r="B524" s="3" t="inlineStr">
+        <is>
+          <t>2,110.03083</t>
+        </is>
+      </c>
+      <c r="C524" s="3" t="inlineStr">
+        <is>
+          <t>Jun 22, 2026</t>
+        </is>
+      </c>
+      <c r="D524" s="3" t="inlineStr">
+        <is>
+          <t>5,554.17965</t>
+        </is>
+      </c>
+      <c r="E524" s="3" t="inlineStr">
+        <is>
+          <t>-35.50429</t>
+        </is>
+      </c>
+      <c r="F524" s="3" t="inlineStr">
+        <is>
+          <t>-85.71414</t>
+        </is>
+      </c>
+      <c r="G524" s="3" t="inlineStr">
+        <is>
+          <t>8,760.668</t>
+        </is>
+      </c>
+      <c r="H524" s="3" t="inlineStr">
+        <is>
+          <t>6,869,078.720</t>
+        </is>
+      </c>
+      <c r="I524" s="3" t="inlineStr">
+        <is>
+          <t>238,925</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I524"/>
+  <dimension ref="A1:I525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25072,6 +25072,53 @@
         </is>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>245,349,386</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>2,127.38127</t>
+        </is>
+      </c>
+      <c r="C525" s="2" t="inlineStr">
+        <is>
+          <t>Jun 23, 2026</t>
+        </is>
+      </c>
+      <c r="D525" s="2" t="inlineStr">
+        <is>
+          <t>5,605.25493</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>17.35044</t>
+        </is>
+      </c>
+      <c r="F525" s="2" t="inlineStr">
+        <is>
+          <t>51.07528</t>
+        </is>
+      </c>
+      <c r="G525" s="2" t="inlineStr">
+        <is>
+          <t>8,283.628</t>
+        </is>
+      </c>
+      <c r="H525" s="2" t="inlineStr">
+        <is>
+          <t>6,902,496.365</t>
+        </is>
+      </c>
+      <c r="I525" s="2" t="inlineStr">
+        <is>
+          <t>206,339</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I525"/>
+  <dimension ref="A1:I526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25119,6 +25119,53 @@
         </is>
       </c>
     </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>266,704,867</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>2,127.48289</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>5,616.83456</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>0.10162</t>
+        </is>
+      </c>
+      <c r="F526" s="2" t="inlineStr">
+        <is>
+          <t>11.57963</t>
+        </is>
+      </c>
+      <c r="G526" s="2" t="inlineStr">
+        <is>
+          <t>9,402.133</t>
+        </is>
+      </c>
+      <c r="H526" s="2" t="inlineStr">
+        <is>
+          <t>6,908,678.625</t>
+        </is>
+      </c>
+      <c r="I526" s="2" t="inlineStr">
+        <is>
+          <t>223,987</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I526"/>
+  <dimension ref="A1:I527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25166,6 +25166,53 @@
         </is>
       </c>
     </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>331,103,078</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <t>2,131.15581</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
+        <is>
+          <t>5,652.82297</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>3.67292</t>
+        </is>
+      </c>
+      <c r="F527" s="2" t="inlineStr">
+        <is>
+          <t>35.98841</t>
+        </is>
+      </c>
+      <c r="G527" s="2" t="inlineStr">
+        <is>
+          <t>11,107.44</t>
+        </is>
+      </c>
+      <c r="H527" s="2" t="inlineStr">
+        <is>
+          <t>6,925,267.933</t>
+        </is>
+      </c>
+      <c r="I527" s="2" t="inlineStr">
+        <is>
+          <t>245,814</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I527"/>
+  <dimension ref="A1:I528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25213,6 +25213,53 @@
         </is>
       </c>
     </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>447,150,782</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>2,162.56909</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>Jun 28, 2026</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>5,719.76404</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>31.41328</t>
+        </is>
+      </c>
+      <c r="F528" s="2" t="inlineStr">
+        <is>
+          <t>66.94107</t>
+        </is>
+      </c>
+      <c r="G528" s="2" t="inlineStr">
+        <is>
+          <t>13,710.383</t>
+        </is>
+      </c>
+      <c r="H528" s="2" t="inlineStr">
+        <is>
+          <t>6,968,093.800</t>
+        </is>
+      </c>
+      <c r="I528" s="2" t="inlineStr">
+        <is>
+          <t>285,232</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I528"/>
+  <dimension ref="A1:I529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25260,6 +25260,53 @@
         </is>
       </c>
     </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>404,233,989</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>2,166.46144</t>
+        </is>
+      </c>
+      <c r="C529" s="2" t="inlineStr">
+        <is>
+          <t>Jun 29, 2026</t>
+        </is>
+      </c>
+      <c r="D529" s="2" t="inlineStr">
+        <is>
+          <t>5,722.5404</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="inlineStr">
+        <is>
+          <t>3.89235</t>
+        </is>
+      </c>
+      <c r="F529" s="2" t="inlineStr">
+        <is>
+          <t>2.77636</t>
+        </is>
+      </c>
+      <c r="G529" s="2" t="inlineStr">
+        <is>
+          <t>13,515.199</t>
+        </is>
+      </c>
+      <c r="H529" s="2" t="inlineStr">
+        <is>
+          <t>6,976,833.672</t>
+        </is>
+      </c>
+      <c r="I529" s="2" t="inlineStr">
+        <is>
+          <t>297,770</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I529"/>
+  <dimension ref="A1:I530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25307,6 +25307,53 @@
         </is>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>474,692,998</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>2,178.38057</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>5,762.83136</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>11.91913</t>
+        </is>
+      </c>
+      <c r="F530" s="2" t="inlineStr">
+        <is>
+          <t>40.29096</t>
+        </is>
+      </c>
+      <c r="G530" s="2" t="inlineStr">
+        <is>
+          <t>15,736.545</t>
+        </is>
+      </c>
+      <c r="H530" s="2" t="inlineStr">
+        <is>
+          <t>6,986,923.053</t>
+        </is>
+      </c>
+      <c r="I530" s="2" t="inlineStr">
+        <is>
+          <t>314,848</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I530"/>
+  <dimension ref="A1:I531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25354,6 +25354,53 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" s="3" t="inlineStr">
+        <is>
+          <t>421,978,491</t>
+        </is>
+      </c>
+      <c r="B531" s="3" t="inlineStr">
+        <is>
+          <t>2,162.01253</t>
+        </is>
+      </c>
+      <c r="C531" s="3" t="inlineStr">
+        <is>
+          <t>Jul 02, 2026</t>
+        </is>
+      </c>
+      <c r="D531" s="3" t="inlineStr">
+        <is>
+          <t>5,743.85884</t>
+        </is>
+      </c>
+      <c r="E531" s="3" t="inlineStr">
+        <is>
+          <t>-16.36804</t>
+        </is>
+      </c>
+      <c r="F531" s="3" t="inlineStr">
+        <is>
+          <t>-18.97252</t>
+        </is>
+      </c>
+      <c r="G531" s="3" t="inlineStr">
+        <is>
+          <t>14,395.45</t>
+        </is>
+      </c>
+      <c r="H531" s="3" t="inlineStr">
+        <is>
+          <t>6,977,391.195</t>
+        </is>
+      </c>
+      <c r="I531" s="3" t="inlineStr">
+        <is>
+          <t>327,405</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I531"/>
+  <dimension ref="A1:I532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25401,6 +25401,53 @@
         </is>
       </c>
     </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>459,942,347</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>2,191.32738</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>Jul 05, 2026</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>5,787.4108</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>29.31485</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>43.55196</t>
+        </is>
+      </c>
+      <c r="G532" s="2" t="inlineStr">
+        <is>
+          <t>15,300.785</t>
+        </is>
+      </c>
+      <c r="H532" s="2" t="inlineStr">
+        <is>
+          <t>6,996,746.023</t>
+        </is>
+      </c>
+      <c r="I532" s="2" t="inlineStr">
+        <is>
+          <t>336,987</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I532"/>
+  <dimension ref="A1:I533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25448,6 +25448,53 @@
         </is>
       </c>
     </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>448,319,793</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>2,192.53234</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>Jul 06, 2026</t>
+        </is>
+      </c>
+      <c r="D533" s="2" t="inlineStr">
+        <is>
+          <t>5,799.51494</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>1.20496</t>
+        </is>
+      </c>
+      <c r="F533" s="2" t="inlineStr">
+        <is>
+          <t>12.10414</t>
+        </is>
+      </c>
+      <c r="G533" s="2" t="inlineStr">
+        <is>
+          <t>14,165.738</t>
+        </is>
+      </c>
+      <c r="H533" s="2" t="inlineStr">
+        <is>
+          <t>7,018,326.292</t>
+        </is>
+      </c>
+      <c r="I533" s="2" t="inlineStr">
+        <is>
+          <t>324,330</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I533"/>
+  <dimension ref="A1:I534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25495,6 +25495,53 @@
         </is>
       </c>
     </row>
+    <row r="534">
+      <c r="A534" s="3" t="inlineStr">
+        <is>
+          <t>452,296,107</t>
+        </is>
+      </c>
+      <c r="B534" s="3" t="inlineStr">
+        <is>
+          <t>2,181.84845</t>
+        </is>
+      </c>
+      <c r="C534" s="3" t="inlineStr">
+        <is>
+          <t>Jul 07, 2026</t>
+        </is>
+      </c>
+      <c r="D534" s="3" t="inlineStr">
+        <is>
+          <t>5,781.27425</t>
+        </is>
+      </c>
+      <c r="E534" s="3" t="inlineStr">
+        <is>
+          <t>-10.68389</t>
+        </is>
+      </c>
+      <c r="F534" s="3" t="inlineStr">
+        <is>
+          <t>-18.24069</t>
+        </is>
+      </c>
+      <c r="G534" s="3" t="inlineStr">
+        <is>
+          <t>13,880.363</t>
+        </is>
+      </c>
+      <c r="H534" s="3" t="inlineStr">
+        <is>
+          <t>7,004,337.827</t>
+        </is>
+      </c>
+      <c r="I534" s="3" t="inlineStr">
+        <is>
+          <t>316,993</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I534"/>
+  <dimension ref="A1:I535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25542,6 +25542,53 @@
         </is>
       </c>
     </row>
+    <row r="535">
+      <c r="A535" s="3" t="inlineStr">
+        <is>
+          <t>403,675,836</t>
+        </is>
+      </c>
+      <c r="B535" s="3" t="inlineStr">
+        <is>
+          <t>2,169.24295</t>
+        </is>
+      </c>
+      <c r="C535" s="3" t="inlineStr">
+        <is>
+          <t>Jul 08, 2026</t>
+        </is>
+      </c>
+      <c r="D535" s="3" t="inlineStr">
+        <is>
+          <t>5,770.27356</t>
+        </is>
+      </c>
+      <c r="E535" s="3" t="inlineStr">
+        <is>
+          <t>-12.6055</t>
+        </is>
+      </c>
+      <c r="F535" s="3" t="inlineStr">
+        <is>
+          <t>-11.00069</t>
+        </is>
+      </c>
+      <c r="G535" s="3" t="inlineStr">
+        <is>
+          <t>11,561.172</t>
+        </is>
+      </c>
+      <c r="H535" s="3" t="inlineStr">
+        <is>
+          <t>7,002,359.413</t>
+        </is>
+      </c>
+      <c r="I535" s="3" t="inlineStr">
+        <is>
+          <t>278,569</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I535"/>
+  <dimension ref="A1:I536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25589,6 +25589,53 @@
         </is>
       </c>
     </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>428,342,460</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>2,177.76114</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>Jul 09, 2026</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>5,804.06354</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>8.51819</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>33.78998</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>14,284.684</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>7,038,343.639</t>
+        </is>
+      </c>
+      <c r="I536" s="2" t="inlineStr">
+        <is>
+          <t>324,776</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I536"/>
+  <dimension ref="A1:I537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25636,6 +25636,53 @@
         </is>
       </c>
     </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>526,885,746</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>2,200.74042</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>Jul 12, 2026</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>5,849.21831</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>22.97928</t>
+        </is>
+      </c>
+      <c r="F537" s="2" t="inlineStr">
+        <is>
+          <t>45.15477</t>
+        </is>
+      </c>
+      <c r="G537" s="2" t="inlineStr">
+        <is>
+          <t>16,696.374</t>
+        </is>
+      </c>
+      <c r="H537" s="2" t="inlineStr">
+        <is>
+          <t>7,059,628.586</t>
+        </is>
+      </c>
+      <c r="I537" s="2" t="inlineStr">
+        <is>
+          <t>382,533</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I537"/>
+  <dimension ref="A1:I538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25683,6 +25683,53 @@
         </is>
       </c>
     </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>437,101,719</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>2,203.09251</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>Jul 13, 2026</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>5,866.54957</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>2.35209</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>17.33126</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>14,191.548</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>7,077,135.115</t>
+        </is>
+      </c>
+      <c r="I538" s="2" t="inlineStr">
+        <is>
+          <t>328,447</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I538"/>
+  <dimension ref="A1:I539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25730,6 +25730,53 @@
         </is>
       </c>
     </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>465,016,276</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>2,227.10021</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>Jul 14, 2026</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>5,911.24296</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>24.0077</t>
+        </is>
+      </c>
+      <c r="F539" s="2" t="inlineStr">
+        <is>
+          <t>44.69339</t>
+        </is>
+      </c>
+      <c r="G539" s="2" t="inlineStr">
+        <is>
+          <t>16,512.915</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="inlineStr">
+        <is>
+          <t>7,107,726.364</t>
+        </is>
+      </c>
+      <c r="I539" s="2" t="inlineStr">
+        <is>
+          <t>356,667</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I539"/>
+  <dimension ref="A1:I540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25777,6 +25777,53 @@
         </is>
       </c>
     </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>417,114,531</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>2,242.90184</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>Jul 15, 2026</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>5,926.27533</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>15.80163</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>15.03237</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>15,159.143</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>7,122,787.277</t>
+        </is>
+      </c>
+      <c r="I540" s="2" t="inlineStr">
+        <is>
+          <t>338,485</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I540"/>
+  <dimension ref="A1:I541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25824,6 +25824,53 @@
         </is>
       </c>
     </row>
+    <row r="541">
+      <c r="A541" s="3" t="inlineStr">
+        <is>
+          <t>334,876,445</t>
+        </is>
+      </c>
+      <c r="B541" s="3" t="inlineStr">
+        <is>
+          <t>2,227.62539</t>
+        </is>
+      </c>
+      <c r="C541" s="3" t="inlineStr">
+        <is>
+          <t>Jul 16, 2026</t>
+        </is>
+      </c>
+      <c r="D541" s="3" t="inlineStr">
+        <is>
+          <t>5,900.35622</t>
+        </is>
+      </c>
+      <c r="E541" s="3" t="inlineStr">
+        <is>
+          <t>-15.27645</t>
+        </is>
+      </c>
+      <c r="F541" s="3" t="inlineStr">
+        <is>
+          <t>-25.91911</t>
+        </is>
+      </c>
+      <c r="G541" s="3" t="inlineStr">
+        <is>
+          <t>11,182.474</t>
+        </is>
+      </c>
+      <c r="H541" s="3" t="inlineStr">
+        <is>
+          <t>7,108,834.199</t>
+        </is>
+      </c>
+      <c r="I541" s="3" t="inlineStr">
+        <is>
+          <t>271,376</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I541"/>
+  <dimension ref="A1:I542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25871,6 +25871,53 @@
         </is>
       </c>
     </row>
+    <row r="542">
+      <c r="A542" s="3" t="inlineStr">
+        <is>
+          <t>354,109,655</t>
+        </is>
+      </c>
+      <c r="B542" s="3" t="inlineStr">
+        <is>
+          <t>2,210.74576</t>
+        </is>
+      </c>
+      <c r="C542" s="3" t="inlineStr">
+        <is>
+          <t>Jul 19, 2026</t>
+        </is>
+      </c>
+      <c r="D542" s="3" t="inlineStr">
+        <is>
+          <t>5,855.7233</t>
+        </is>
+      </c>
+      <c r="E542" s="3" t="inlineStr">
+        <is>
+          <t>-16.87963</t>
+        </is>
+      </c>
+      <c r="F542" s="3" t="inlineStr">
+        <is>
+          <t>-44.63292</t>
+        </is>
+      </c>
+      <c r="G542" s="3" t="inlineStr">
+        <is>
+          <t>10,703.95</t>
+        </is>
+      </c>
+      <c r="H542" s="3" t="inlineStr">
+        <is>
+          <t>7,082,582.537</t>
+        </is>
+      </c>
+      <c r="I542" s="3" t="inlineStr">
+        <is>
+          <t>277,180</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I542"/>
+  <dimension ref="A1:I543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25918,6 +25918,53 @@
         </is>
       </c>
     </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>333,042,551</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>2,208.83905</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>Jul 20, 2026</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>5,857.62331</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>-1.90671</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>1.90001</t>
+        </is>
+      </c>
+      <c r="G543" s="2" t="inlineStr">
+        <is>
+          <t>9,665.318</t>
+        </is>
+      </c>
+      <c r="H543" s="2" t="inlineStr">
+        <is>
+          <t>7,068,250.078</t>
+        </is>
+      </c>
+      <c r="I543" s="2" t="inlineStr">
+        <is>
+          <t>254,077</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I543"/>
+  <dimension ref="A1:I544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25965,6 +25965,53 @@
         </is>
       </c>
     </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>456,959,944</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>2,220.00104</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>Jul 21, 2026</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>5,898.9642</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>11.16199</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>41.34089</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>11,293.963</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>7,074,821.629</t>
+        </is>
+      </c>
+      <c r="I544" s="2" t="inlineStr">
+        <is>
+          <t>265,358</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I544"/>
+  <dimension ref="A1:I545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26012,6 +26012,53 @@
         </is>
       </c>
     </row>
+    <row r="545">
+      <c r="A545" s="3" t="inlineStr">
+        <is>
+          <t>517,183,378</t>
+        </is>
+      </c>
+      <c r="B545" s="3" t="inlineStr">
+        <is>
+          <t>2,216.65361</t>
+        </is>
+      </c>
+      <c r="C545" s="3" t="inlineStr">
+        <is>
+          <t>Jul 22, 2026</t>
+        </is>
+      </c>
+      <c r="D545" s="3" t="inlineStr">
+        <is>
+          <t>5,871.06459</t>
+        </is>
+      </c>
+      <c r="E545" s="3" t="inlineStr">
+        <is>
+          <t>-3.34743</t>
+        </is>
+      </c>
+      <c r="F545" s="3" t="inlineStr">
+        <is>
+          <t>-27.89961</t>
+        </is>
+      </c>
+      <c r="G545" s="3" t="inlineStr">
+        <is>
+          <t>12,111.307</t>
+        </is>
+      </c>
+      <c r="H545" s="3" t="inlineStr">
+        <is>
+          <t>7,055,694.699</t>
+        </is>
+      </c>
+      <c r="I545" s="3" t="inlineStr">
+        <is>
+          <t>294,367</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I545"/>
+  <dimension ref="A1:I546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26059,6 +26059,53 @@
         </is>
       </c>
     </row>
+    <row r="546">
+      <c r="A546" s="3" t="inlineStr">
+        <is>
+          <t>412,214,217</t>
+        </is>
+      </c>
+      <c r="B546" s="3" t="inlineStr">
+        <is>
+          <t>2,192.72247</t>
+        </is>
+      </c>
+      <c r="C546" s="3" t="inlineStr">
+        <is>
+          <t>Jul 23, 2026</t>
+        </is>
+      </c>
+      <c r="D546" s="3" t="inlineStr">
+        <is>
+          <t>5,804.29742</t>
+        </is>
+      </c>
+      <c r="E546" s="3" t="inlineStr">
+        <is>
+          <t>-23.93114</t>
+        </is>
+      </c>
+      <c r="F546" s="3" t="inlineStr">
+        <is>
+          <t>-66.76717</t>
+        </is>
+      </c>
+      <c r="G546" s="3" t="inlineStr">
+        <is>
+          <t>9,388.808</t>
+        </is>
+      </c>
+      <c r="H546" s="3" t="inlineStr">
+        <is>
+          <t>7,012,708.629</t>
+        </is>
+      </c>
+      <c r="I546" s="3" t="inlineStr">
+        <is>
+          <t>249,005</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I546"/>
+  <dimension ref="A1:I547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26106,6 +26106,53 @@
         </is>
       </c>
     </row>
+    <row r="547">
+      <c r="A547" s="3" t="inlineStr">
+        <is>
+          <t>310,350,039</t>
+        </is>
+      </c>
+      <c r="B547" s="3" t="inlineStr">
+        <is>
+          <t>2,186.20864</t>
+        </is>
+      </c>
+      <c r="C547" s="3" t="inlineStr">
+        <is>
+          <t>Jul 26, 2026</t>
+        </is>
+      </c>
+      <c r="D547" s="3" t="inlineStr">
+        <is>
+          <t>5,784.36902</t>
+        </is>
+      </c>
+      <c r="E547" s="3" t="inlineStr">
+        <is>
+          <t>-6.51383</t>
+        </is>
+      </c>
+      <c r="F547" s="3" t="inlineStr">
+        <is>
+          <t>-19.9284</t>
+        </is>
+      </c>
+      <c r="G547" s="3" t="inlineStr">
+        <is>
+          <t>7,806.391</t>
+        </is>
+      </c>
+      <c r="H547" s="3" t="inlineStr">
+        <is>
+          <t>6,988,907.220</t>
+        </is>
+      </c>
+      <c r="I547" s="3" t="inlineStr">
+        <is>
+          <t>227,923</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I547"/>
+  <dimension ref="A1:I548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26153,6 +26153,53 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>370,738,837</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>2,201.56348</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>Jul 27, 2026</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>5,839.77166</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>15.35484</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>55.40264</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="inlineStr">
+        <is>
+          <t>8,720.899</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>7,021,197.249</t>
+        </is>
+      </c>
+      <c r="I548" s="2" t="inlineStr">
+        <is>
+          <t>215,895</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I548"/>
+  <dimension ref="A1:I549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26200,6 +26200,53 @@
         </is>
       </c>
     </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>491,872,583</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>2,219.49419</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>Jul 28, 2026</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>5,900.26578</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>17.93071</t>
+        </is>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
+        <is>
+          <t>60.49412</t>
+        </is>
+      </c>
+      <c r="G549" s="2" t="inlineStr">
+        <is>
+          <t>12,609.304</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="inlineStr">
+        <is>
+          <t>7,049,173.548</t>
+        </is>
+      </c>
+      <c r="I549" s="2" t="inlineStr">
+        <is>
+          <t>278,917</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I549"/>
+  <dimension ref="A1:I550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26247,6 +26247,53 @@
         </is>
       </c>
     </row>
+    <row r="550">
+      <c r="A550" s="3" t="inlineStr">
+        <is>
+          <t>505,039,949</t>
+        </is>
+      </c>
+      <c r="B550" s="3" t="inlineStr">
+        <is>
+          <t>2,210.72847</t>
+        </is>
+      </c>
+      <c r="C550" s="3" t="inlineStr">
+        <is>
+          <t>Jul 29, 2026</t>
+        </is>
+      </c>
+      <c r="D550" s="3" t="inlineStr">
+        <is>
+          <t>5,878.85336</t>
+        </is>
+      </c>
+      <c r="E550" s="3" t="inlineStr">
+        <is>
+          <t>-8.76572</t>
+        </is>
+      </c>
+      <c r="F550" s="3" t="inlineStr">
+        <is>
+          <t>-21.41242</t>
+        </is>
+      </c>
+      <c r="G550" s="3" t="inlineStr">
+        <is>
+          <t>13,425.17</t>
+        </is>
+      </c>
+      <c r="H550" s="3" t="inlineStr">
+        <is>
+          <t>7,040,765.772</t>
+        </is>
+      </c>
+      <c r="I550" s="3" t="inlineStr">
+        <is>
+          <t>311,860</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I550"/>
+  <dimension ref="A1:I551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26294,6 +26294,53 @@
         </is>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>388,507,319</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>2,217.22332</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>Jul 30, 2026</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>5,895.583</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>6.49485</t>
+        </is>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>16.72964</t>
+        </is>
+      </c>
+      <c r="G551" s="2" t="inlineStr">
+        <is>
+          <t>10,434.355</t>
+        </is>
+      </c>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>7,051,339.380</t>
+        </is>
+      </c>
+      <c r="I551" s="2" t="inlineStr">
+        <is>
+          <t>247,542</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I551"/>
+  <dimension ref="A1:I552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26341,6 +26341,53 @@
         </is>
       </c>
     </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>514,332,217</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>2,213.33536</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>Aug 02, 2026</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>5,895.78358</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>-3.88796</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>0.20058</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="inlineStr">
+        <is>
+          <t>12,576.233</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>7,061,147.633</t>
+        </is>
+      </c>
+      <c r="I552" s="2" t="inlineStr">
+        <is>
+          <t>291,079</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I552"/>
+  <dimension ref="A1:I553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26388,6 +26388,53 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" s="3" t="inlineStr">
+        <is>
+          <t>488,399,081</t>
+        </is>
+      </c>
+      <c r="B553" s="3" t="inlineStr">
+        <is>
+          <t>2,204.17056</t>
+        </is>
+      </c>
+      <c r="C553" s="3" t="inlineStr">
+        <is>
+          <t>Aug 03, 2026</t>
+        </is>
+      </c>
+      <c r="D553" s="3" t="inlineStr">
+        <is>
+          <t>5,885.69199</t>
+        </is>
+      </c>
+      <c r="E553" s="3" t="inlineStr">
+        <is>
+          <t>-9.1648</t>
+        </is>
+      </c>
+      <c r="F553" s="3" t="inlineStr">
+        <is>
+          <t>-10.09159</t>
+        </is>
+      </c>
+      <c r="G553" s="3" t="inlineStr">
+        <is>
+          <t>12,105.195</t>
+        </is>
+      </c>
+      <c r="H553" s="3" t="inlineStr">
+        <is>
+          <t>7,080,036.179</t>
+        </is>
+      </c>
+      <c r="I553" s="3" t="inlineStr">
+        <is>
+          <t>275,288</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I553"/>
+  <dimension ref="A1:I554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26435,6 +26435,53 @@
         </is>
       </c>
     </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>440,642,838</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>2,201.74906</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>Aug 04, 2026</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>5,894.12702</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>-2.4215</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>8.43503</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>11,114.929</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>7,104,492.030</t>
+        </is>
+      </c>
+      <c r="I554" s="2" t="inlineStr">
+        <is>
+          <t>268,395</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I554"/>
+  <dimension ref="A1:I555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26482,6 +26482,53 @@
         </is>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" s="3" t="inlineStr">
+        <is>
+          <t>411,801,570</t>
+        </is>
+      </c>
+      <c r="B555" s="3" t="inlineStr">
+        <is>
+          <t>2,191.84674</t>
+        </is>
+      </c>
+      <c r="C555" s="3" t="inlineStr">
+        <is>
+          <t>Aug 06, 2026</t>
+        </is>
+      </c>
+      <c r="D555" s="3" t="inlineStr">
+        <is>
+          <t>5,860.95785</t>
+        </is>
+      </c>
+      <c r="E555" s="3" t="inlineStr">
+        <is>
+          <t>-9.90232</t>
+        </is>
+      </c>
+      <c r="F555" s="3" t="inlineStr">
+        <is>
+          <t>-33.16917</t>
+        </is>
+      </c>
+      <c r="G555" s="3" t="inlineStr">
+        <is>
+          <t>11,477.414</t>
+        </is>
+      </c>
+      <c r="H555" s="3" t="inlineStr">
+        <is>
+          <t>7,079,146.963</t>
+        </is>
+      </c>
+      <c r="I555" s="3" t="inlineStr">
+        <is>
+          <t>274,233</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I555"/>
+  <dimension ref="A1:I556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26529,6 +26529,53 @@
         </is>
       </c>
     </row>
+    <row r="556">
+      <c r="A556" s="3" t="inlineStr">
+        <is>
+          <t>331,970,351</t>
+        </is>
+      </c>
+      <c r="B556" s="3" t="inlineStr">
+        <is>
+          <t>2,177.28917</t>
+        </is>
+      </c>
+      <c r="C556" s="3" t="inlineStr">
+        <is>
+          <t>Aug 09, 2026</t>
+        </is>
+      </c>
+      <c r="D556" s="3" t="inlineStr">
+        <is>
+          <t>5,822.3182</t>
+        </is>
+      </c>
+      <c r="E556" s="3" t="inlineStr">
+        <is>
+          <t>-14.55757</t>
+        </is>
+      </c>
+      <c r="F556" s="3" t="inlineStr">
+        <is>
+          <t>-38.63965</t>
+        </is>
+      </c>
+      <c r="G556" s="3" t="inlineStr">
+        <is>
+          <t>9,645.915</t>
+        </is>
+      </c>
+      <c r="H556" s="3" t="inlineStr">
+        <is>
+          <t>7,031,022.092</t>
+        </is>
+      </c>
+      <c r="I556" s="3" t="inlineStr">
+        <is>
+          <t>245,942</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I556"/>
+  <dimension ref="A1:I557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26576,6 +26576,53 @@
         </is>
       </c>
     </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>324,301,844</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>2,185.85315</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>Aug 10, 2026</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>5,844.87198</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>8.56398</t>
+        </is>
+      </c>
+      <c r="F557" s="2" t="inlineStr">
+        <is>
+          <t>22.55378</t>
+        </is>
+      </c>
+      <c r="G557" s="2" t="inlineStr">
+        <is>
+          <t>9,084.031</t>
+        </is>
+      </c>
+      <c r="H557" s="2" t="inlineStr">
+        <is>
+          <t>7,054,953.655</t>
+        </is>
+      </c>
+      <c r="I557" s="2" t="inlineStr">
+        <is>
+          <t>225,976</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I557"/>
+  <dimension ref="A1:I558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26623,6 +26623,53 @@
         </is>
       </c>
     </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>411,484,560</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>2,204.56937</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>5,903.53106</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>18.71622</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>58.65908</t>
+        </is>
+      </c>
+      <c r="G558" s="2" t="inlineStr">
+        <is>
+          <t>11,154.267</t>
+        </is>
+      </c>
+      <c r="H558" s="2" t="inlineStr">
+        <is>
+          <t>7,087,810.557</t>
+        </is>
+      </c>
+      <c r="I558" s="2" t="inlineStr">
+        <is>
+          <t>260,288</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I558"/>
+  <dimension ref="A1:I559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26670,6 +26670,53 @@
         </is>
       </c>
     </row>
+    <row r="559">
+      <c r="A559" s="3" t="inlineStr">
+        <is>
+          <t>369,825,385</t>
+        </is>
+      </c>
+      <c r="B559" s="3" t="inlineStr">
+        <is>
+          <t>2,200.49605</t>
+        </is>
+      </c>
+      <c r="C559" s="3" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="D559" s="3" t="inlineStr">
+        <is>
+          <t>5,897.27422</t>
+        </is>
+      </c>
+      <c r="E559" s="3" t="inlineStr">
+        <is>
+          <t>-4.07332</t>
+        </is>
+      </c>
+      <c r="F559" s="3" t="inlineStr">
+        <is>
+          <t>-6.25684</t>
+        </is>
+      </c>
+      <c r="G559" s="3" t="inlineStr">
+        <is>
+          <t>10,737.306</t>
+        </is>
+      </c>
+      <c r="H559" s="3" t="inlineStr">
+        <is>
+          <t>7,081,922.097</t>
+        </is>
+      </c>
+      <c r="I559" s="3" t="inlineStr">
+        <is>
+          <t>267,674</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I559"/>
+  <dimension ref="A1:I560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26717,6 +26717,53 @@
         </is>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" s="3" t="inlineStr">
+        <is>
+          <t>299,233,097</t>
+        </is>
+      </c>
+      <c r="B560" s="3" t="inlineStr">
+        <is>
+          <t>2,192.73486</t>
+        </is>
+      </c>
+      <c r="C560" s="3" t="inlineStr">
+        <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="D560" s="3" t="inlineStr">
+        <is>
+          <t>5,883.91339</t>
+        </is>
+      </c>
+      <c r="E560" s="3" t="inlineStr">
+        <is>
+          <t>-7.76119</t>
+        </is>
+      </c>
+      <c r="F560" s="3" t="inlineStr">
+        <is>
+          <t>-13.36083</t>
+        </is>
+      </c>
+      <c r="G560" s="3" t="inlineStr">
+        <is>
+          <t>9,256.692</t>
+        </is>
+      </c>
+      <c r="H560" s="3" t="inlineStr">
+        <is>
+          <t>7,076,155.289</t>
+        </is>
+      </c>
+      <c r="I560" s="3" t="inlineStr">
+        <is>
+          <t>239,663</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I560"/>
+  <dimension ref="A1:I561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26764,6 +26764,53 @@
         </is>
       </c>
     </row>
+    <row r="561">
+      <c r="A561" s="3" t="inlineStr">
+        <is>
+          <t>362,273,077</t>
+        </is>
+      </c>
+      <c r="B561" s="3" t="inlineStr">
+        <is>
+          <t>2,184.22288</t>
+        </is>
+      </c>
+      <c r="C561" s="3" t="inlineStr">
+        <is>
+          <t>Aug 16, 2026</t>
+        </is>
+      </c>
+      <c r="D561" s="3" t="inlineStr">
+        <is>
+          <t>5,859.97953</t>
+        </is>
+      </c>
+      <c r="E561" s="3" t="inlineStr">
+        <is>
+          <t>-8.51198</t>
+        </is>
+      </c>
+      <c r="F561" s="3" t="inlineStr">
+        <is>
+          <t>-23.93386</t>
+        </is>
+      </c>
+      <c r="G561" s="3" t="inlineStr">
+        <is>
+          <t>11,307.671</t>
+        </is>
+      </c>
+      <c r="H561" s="3" t="inlineStr">
+        <is>
+          <t>7,082,499.226</t>
+        </is>
+      </c>
+      <c r="I561" s="3" t="inlineStr">
+        <is>
+          <t>281,665</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I561"/>
+  <dimension ref="A1:I562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26811,6 +26811,53 @@
         </is>
       </c>
     </row>
+    <row r="562">
+      <c r="A562" s="3" t="inlineStr">
+        <is>
+          <t>349,534,151</t>
+        </is>
+      </c>
+      <c r="B562" s="3" t="inlineStr">
+        <is>
+          <t>2,175.66117</t>
+        </is>
+      </c>
+      <c r="C562" s="3" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="D562" s="3" t="inlineStr">
+        <is>
+          <t>5,814.26969</t>
+        </is>
+      </c>
+      <c r="E562" s="3" t="inlineStr">
+        <is>
+          <t>-8.56171</t>
+        </is>
+      </c>
+      <c r="F562" s="3" t="inlineStr">
+        <is>
+          <t>-45.70984</t>
+        </is>
+      </c>
+      <c r="G562" s="3" t="inlineStr">
+        <is>
+          <t>9,948.55</t>
+        </is>
+      </c>
+      <c r="H562" s="3" t="inlineStr">
+        <is>
+          <t>7,051,878.923</t>
+        </is>
+      </c>
+      <c r="I562" s="3" t="inlineStr">
+        <is>
+          <t>261,007</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I562"/>
+  <dimension ref="A1:I563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26858,6 +26858,53 @@
         </is>
       </c>
     </row>
+    <row r="563">
+      <c r="A563" s="3" t="inlineStr">
+        <is>
+          <t>318,865,896</t>
+        </is>
+      </c>
+      <c r="B563" s="3" t="inlineStr">
+        <is>
+          <t>2,164.46791</t>
+        </is>
+      </c>
+      <c r="C563" s="3" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="D563" s="3" t="inlineStr">
+        <is>
+          <t>5,773.62948</t>
+        </is>
+      </c>
+      <c r="E563" s="3" t="inlineStr">
+        <is>
+          <t>-11.19326</t>
+        </is>
+      </c>
+      <c r="F563" s="3" t="inlineStr">
+        <is>
+          <t>-40.64021</t>
+        </is>
+      </c>
+      <c r="G563" s="3" t="inlineStr">
+        <is>
+          <t>9,981.092</t>
+        </is>
+      </c>
+      <c r="H563" s="3" t="inlineStr">
+        <is>
+          <t>7,029,871.326</t>
+        </is>
+      </c>
+      <c r="I563" s="3" t="inlineStr">
+        <is>
+          <t>247,783</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I563"/>
+  <dimension ref="A1:I564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26905,6 +26905,53 @@
         </is>
       </c>
     </row>
+    <row r="564">
+      <c r="A564" s="3" t="inlineStr">
+        <is>
+          <t>248,066,216</t>
+        </is>
+      </c>
+      <c r="B564" s="3" t="inlineStr">
+        <is>
+          <t>2,162.96711</t>
+        </is>
+      </c>
+      <c r="C564" s="3" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="D564" s="3" t="inlineStr">
+        <is>
+          <t>5,769.7108</t>
+        </is>
+      </c>
+      <c r="E564" s="3" t="inlineStr">
+        <is>
+          <t>-1.5008</t>
+        </is>
+      </c>
+      <c r="F564" s="3" t="inlineStr">
+        <is>
+          <t>-3.91868</t>
+        </is>
+      </c>
+      <c r="G564" s="3" t="inlineStr">
+        <is>
+          <t>7,328.318</t>
+        </is>
+      </c>
+      <c r="H564" s="3" t="inlineStr">
+        <is>
+          <t>7,014,074.597</t>
+        </is>
+      </c>
+      <c r="I564" s="3" t="inlineStr">
+        <is>
+          <t>205,886</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I564"/>
+  <dimension ref="A1:I565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26952,6 +26952,53 @@
         </is>
       </c>
     </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>224,179,101</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>2,162.51961</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>Aug 20, 2026</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>5,786.08054</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="inlineStr">
+        <is>
+          <t>-0.4475</t>
+        </is>
+      </c>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>16.36974</t>
+        </is>
+      </c>
+      <c r="G565" s="2" t="inlineStr">
+        <is>
+          <t>6,719.891</t>
+        </is>
+      </c>
+      <c r="H565" s="2" t="inlineStr">
+        <is>
+          <t>7,038,122.976</t>
+        </is>
+      </c>
+      <c r="I565" s="2" t="inlineStr">
+        <is>
+          <t>183,066</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I565"/>
+  <dimension ref="A1:I566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26999,6 +26999,53 @@
         </is>
       </c>
     </row>
+    <row r="566">
+      <c r="A566" s="3" t="inlineStr">
+        <is>
+          <t>250,250,134</t>
+        </is>
+      </c>
+      <c r="B566" s="3" t="inlineStr">
+        <is>
+          <t>2,145.48199</t>
+        </is>
+      </c>
+      <c r="C566" s="3" t="inlineStr">
+        <is>
+          <t>Aug 23, 2026</t>
+        </is>
+      </c>
+      <c r="D566" s="3" t="inlineStr">
+        <is>
+          <t>5,722.21464</t>
+        </is>
+      </c>
+      <c r="E566" s="3" t="inlineStr">
+        <is>
+          <t>-17.03762</t>
+        </is>
+      </c>
+      <c r="F566" s="3" t="inlineStr">
+        <is>
+          <t>-63.8659</t>
+        </is>
+      </c>
+      <c r="G566" s="3" t="inlineStr">
+        <is>
+          <t>7,111.497</t>
+        </is>
+      </c>
+      <c r="H566" s="3" t="inlineStr">
+        <is>
+          <t>7,004,085.875</t>
+        </is>
+      </c>
+      <c r="I566" s="3" t="inlineStr">
+        <is>
+          <t>204,263</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I566"/>
+  <dimension ref="A1:I567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27046,6 +27046,53 @@
         </is>
       </c>
     </row>
+    <row r="567">
+      <c r="A567" s="3" t="inlineStr">
+        <is>
+          <t>225,057,197</t>
+        </is>
+      </c>
+      <c r="B567" s="3" t="inlineStr">
+        <is>
+          <t>2,130.84333</t>
+        </is>
+      </c>
+      <c r="C567" s="3" t="inlineStr">
+        <is>
+          <t>Aug 24, 2026</t>
+        </is>
+      </c>
+      <c r="D567" s="3" t="inlineStr">
+        <is>
+          <t>5,643.56975</t>
+        </is>
+      </c>
+      <c r="E567" s="3" t="inlineStr">
+        <is>
+          <t>-14.63866</t>
+        </is>
+      </c>
+      <c r="F567" s="3" t="inlineStr">
+        <is>
+          <t>-78.64489</t>
+        </is>
+      </c>
+      <c r="G567" s="3" t="inlineStr">
+        <is>
+          <t>6,019.725</t>
+        </is>
+      </c>
+      <c r="H567" s="3" t="inlineStr">
+        <is>
+          <t>6,957,361.094</t>
+        </is>
+      </c>
+      <c r="I567" s="3" t="inlineStr">
+        <is>
+          <t>191,943</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I567"/>
+  <dimension ref="A1:I568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27093,6 +27093,53 @@
         </is>
       </c>
     </row>
+    <row r="568">
+      <c r="A568" s="3" t="inlineStr">
+        <is>
+          <t>191,683,061</t>
+        </is>
+      </c>
+      <c r="B568" s="3" t="inlineStr">
+        <is>
+          <t>2,126.11185</t>
+        </is>
+      </c>
+      <c r="C568" s="3" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="D568" s="3" t="inlineStr">
+        <is>
+          <t>5,640.08828</t>
+        </is>
+      </c>
+      <c r="E568" s="3" t="inlineStr">
+        <is>
+          <t>-4.73148</t>
+        </is>
+      </c>
+      <c r="F568" s="3" t="inlineStr">
+        <is>
+          <t>-3.48147</t>
+        </is>
+      </c>
+      <c r="G568" s="3" t="inlineStr">
+        <is>
+          <t>5,067.175</t>
+        </is>
+      </c>
+      <c r="H568" s="3" t="inlineStr">
+        <is>
+          <t>6,954,787.414</t>
+        </is>
+      </c>
+      <c r="I568" s="3" t="inlineStr">
+        <is>
+          <t>154,602</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I568"/>
+  <dimension ref="A1:I569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27140,6 +27140,53 @@
         </is>
       </c>
     </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>177,465,534</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>2,134.8839</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>Aug 27, 2026</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>5,655.68313</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr">
+        <is>
+          <t>8.77205</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
+          <t>15.59485</t>
+        </is>
+      </c>
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>4,670.148</t>
+        </is>
+      </c>
+      <c r="H569" s="2" t="inlineStr">
+        <is>
+          <t>6,973,182.358</t>
+        </is>
+      </c>
+      <c r="I569" s="2" t="inlineStr">
+        <is>
+          <t>147,461</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I569"/>
+  <dimension ref="A1:I570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27187,6 +27187,53 @@
         </is>
       </c>
     </row>
+    <row r="570">
+      <c r="A570" s="3" t="inlineStr">
+        <is>
+          <t>189,870,724</t>
+        </is>
+      </c>
+      <c r="B570" s="3" t="inlineStr">
+        <is>
+          <t>2,122.22834</t>
+        </is>
+      </c>
+      <c r="C570" s="3" t="inlineStr">
+        <is>
+          <t>Aug 30, 2026</t>
+        </is>
+      </c>
+      <c r="D570" s="3" t="inlineStr">
+        <is>
+          <t>5,614.28889</t>
+        </is>
+      </c>
+      <c r="E570" s="3" t="inlineStr">
+        <is>
+          <t>-12.65556</t>
+        </is>
+      </c>
+      <c r="F570" s="3" t="inlineStr">
+        <is>
+          <t>-41.39424</t>
+        </is>
+      </c>
+      <c r="G570" s="3" t="inlineStr">
+        <is>
+          <t>5,180.307</t>
+        </is>
+      </c>
+      <c r="H570" s="3" t="inlineStr">
+        <is>
+          <t>6,958,408.522</t>
+        </is>
+      </c>
+      <c r="I570" s="3" t="inlineStr">
+        <is>
+          <t>163,315</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I570"/>
+  <dimension ref="A1:I571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27234,6 +27234,53 @@
         </is>
       </c>
     </row>
+    <row r="571">
+      <c r="A571" s="3" t="inlineStr">
+        <is>
+          <t>177,515,959</t>
+        </is>
+      </c>
+      <c r="B571" s="3" t="inlineStr">
+        <is>
+          <t>2,113.24289</t>
+        </is>
+      </c>
+      <c r="C571" s="3" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="D571" s="3" t="inlineStr">
+        <is>
+          <t>5,598.08155</t>
+        </is>
+      </c>
+      <c r="E571" s="3" t="inlineStr">
+        <is>
+          <t>-8.98545</t>
+        </is>
+      </c>
+      <c r="F571" s="3" t="inlineStr">
+        <is>
+          <t>-16.20734</t>
+        </is>
+      </c>
+      <c r="G571" s="3" t="inlineStr">
+        <is>
+          <t>4,772.465</t>
+        </is>
+      </c>
+      <c r="H571" s="3" t="inlineStr">
+        <is>
+          <t>6,947,392.560</t>
+        </is>
+      </c>
+      <c r="I571" s="3" t="inlineStr">
+        <is>
+          <t>149,199</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I571"/>
+  <dimension ref="A1:I572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27281,6 +27281,53 @@
         </is>
       </c>
     </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>205,817,451</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>2,122.03872</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>5,637.30496</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>8.79583</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>39.22341</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>5,968.225</t>
+        </is>
+      </c>
+      <c r="H572" s="2" t="inlineStr">
+        <is>
+          <t>6,976,342.202</t>
+        </is>
+      </c>
+      <c r="I572" s="2" t="inlineStr">
+        <is>
+          <t>150,064</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I572"/>
+  <dimension ref="A1:I573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27328,6 +27328,53 @@
         </is>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>255,526,268</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>2,125.4871</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>5,660.41404</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="inlineStr">
+        <is>
+          <t>3.44838</t>
+        </is>
+      </c>
+      <c r="F573" s="2" t="inlineStr">
+        <is>
+          <t>23.10908</t>
+        </is>
+      </c>
+      <c r="G573" s="2" t="inlineStr">
+        <is>
+          <t>7,310.739</t>
+        </is>
+      </c>
+      <c r="H573" s="2" t="inlineStr">
+        <is>
+          <t>6,985,593.474</t>
+        </is>
+      </c>
+      <c r="I573" s="2" t="inlineStr">
+        <is>
+          <t>175,097</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I573"/>
+  <dimension ref="A1:I574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27375,6 +27375,53 @@
         </is>
       </c>
     </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>234,826,254</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>2,140.73161</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>5,662.09008</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>15.24451</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>1.67604</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="inlineStr">
+        <is>
+          <t>7,209.212</t>
+        </is>
+      </c>
+      <c r="H574" s="2" t="inlineStr">
+        <is>
+          <t>6,984,977.894</t>
+        </is>
+      </c>
+      <c r="I574" s="2" t="inlineStr">
+        <is>
+          <t>197,767</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I574"/>
+  <dimension ref="A1:I575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27422,6 +27422,53 @@
         </is>
       </c>
     </row>
+    <row r="575">
+      <c r="A575" s="3" t="inlineStr">
+        <is>
+          <t>204,341,869</t>
+        </is>
+      </c>
+      <c r="B575" s="3" t="inlineStr">
+        <is>
+          <t>2,116.19617</t>
+        </is>
+      </c>
+      <c r="C575" s="3" t="inlineStr">
+        <is>
+          <t>Sep 06, 2026</t>
+        </is>
+      </c>
+      <c r="D575" s="3" t="inlineStr">
+        <is>
+          <t>5,558.44526</t>
+        </is>
+      </c>
+      <c r="E575" s="3" t="inlineStr">
+        <is>
+          <t>-24.53544</t>
+        </is>
+      </c>
+      <c r="F575" s="3" t="inlineStr">
+        <is>
+          <t>-103.64482</t>
+        </is>
+      </c>
+      <c r="G575" s="3" t="inlineStr">
+        <is>
+          <t>5,452.768</t>
+        </is>
+      </c>
+      <c r="H575" s="3" t="inlineStr">
+        <is>
+          <t>6,917,160.140</t>
+        </is>
+      </c>
+      <c r="I575" s="3" t="inlineStr">
+        <is>
+          <t>178,150</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I575"/>
+  <dimension ref="A1:I576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27469,6 +27469,53 @@
         </is>
       </c>
     </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>200,350,191</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>2,113.92338</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>Sep 07, 2026</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>5,567.42309</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>-2.27279</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>8.97783</t>
+        </is>
+      </c>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
+          <t>5,713.246</t>
+        </is>
+      </c>
+      <c r="H576" s="2" t="inlineStr">
+        <is>
+          <t>6,915,220.867</t>
+        </is>
+      </c>
+      <c r="I576" s="2" t="inlineStr">
+        <is>
+          <t>185,987</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I576"/>
+  <dimension ref="A1:I577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27516,6 +27516,53 @@
         </is>
       </c>
     </row>
+    <row r="577">
+      <c r="A577" s="3" t="inlineStr">
+        <is>
+          <t>191,268,628</t>
+        </is>
+      </c>
+      <c r="B577" s="3" t="inlineStr">
+        <is>
+          <t>2,108.26982</t>
+        </is>
+      </c>
+      <c r="C577" s="3" t="inlineStr">
+        <is>
+          <t>Sep 08, 2026</t>
+        </is>
+      </c>
+      <c r="D577" s="3" t="inlineStr">
+        <is>
+          <t>5,539.32016</t>
+        </is>
+      </c>
+      <c r="E577" s="3" t="inlineStr">
+        <is>
+          <t>-5.65356</t>
+        </is>
+      </c>
+      <c r="F577" s="3" t="inlineStr">
+        <is>
+          <t>-28.10293</t>
+        </is>
+      </c>
+      <c r="G577" s="3" t="inlineStr">
+        <is>
+          <t>5,904.379</t>
+        </is>
+      </c>
+      <c r="H577" s="3" t="inlineStr">
+        <is>
+          <t>6,911,303.853</t>
+        </is>
+      </c>
+      <c r="I577" s="3" t="inlineStr">
+        <is>
+          <t>168,534</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I577"/>
+  <dimension ref="A1:I578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27563,6 +27563,53 @@
         </is>
       </c>
     </row>
+    <row r="578">
+      <c r="A578" s="3" t="inlineStr">
+        <is>
+          <t>183,505,470</t>
+        </is>
+      </c>
+      <c r="B578" s="3" t="inlineStr">
+        <is>
+          <t>2,103.03041</t>
+        </is>
+      </c>
+      <c r="C578" s="3" t="inlineStr">
+        <is>
+          <t>Sep 09, 2026</t>
+        </is>
+      </c>
+      <c r="D578" s="3" t="inlineStr">
+        <is>
+          <t>5,537.8767</t>
+        </is>
+      </c>
+      <c r="E578" s="3" t="inlineStr">
+        <is>
+          <t>-5.23941</t>
+        </is>
+      </c>
+      <c r="F578" s="3" t="inlineStr">
+        <is>
+          <t>-1.44346</t>
+        </is>
+      </c>
+      <c r="G578" s="3" t="inlineStr">
+        <is>
+          <t>5,197.785</t>
+        </is>
+      </c>
+      <c r="H578" s="3" t="inlineStr">
+        <is>
+          <t>6,930,895.700</t>
+        </is>
+      </c>
+      <c r="I578" s="3" t="inlineStr">
+        <is>
+          <t>148,936</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I578"/>
+  <dimension ref="A1:I579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27610,6 +27610,53 @@
         </is>
       </c>
     </row>
+    <row r="579">
+      <c r="A579" s="3" t="inlineStr">
+        <is>
+          <t>217,642,066</t>
+        </is>
+      </c>
+      <c r="B579" s="3" t="inlineStr">
+        <is>
+          <t>2,095.3105</t>
+        </is>
+      </c>
+      <c r="C579" s="3" t="inlineStr">
+        <is>
+          <t>Sep 10, 2026</t>
+        </is>
+      </c>
+      <c r="D579" s="3" t="inlineStr">
+        <is>
+          <t>5,515.16816</t>
+        </is>
+      </c>
+      <c r="E579" s="3" t="inlineStr">
+        <is>
+          <t>-7.71991</t>
+        </is>
+      </c>
+      <c r="F579" s="3" t="inlineStr">
+        <is>
+          <t>-22.70854</t>
+        </is>
+      </c>
+      <c r="G579" s="3" t="inlineStr">
+        <is>
+          <t>5,444.257</t>
+        </is>
+      </c>
+      <c r="H579" s="3" t="inlineStr">
+        <is>
+          <t>6,930,680.150</t>
+        </is>
+      </c>
+      <c r="I579" s="3" t="inlineStr">
+        <is>
+          <t>156,869</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
